--- a/data/trans_orig/P16A09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>465657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>467489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>959686</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>961553</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>731324</t>
+          <t>730701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>614110</t>
+          <t>615378</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1348609</t>
+          <t>1350044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360030</t>
+          <t>1360037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635652</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637649</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673944</t>
+          <t>674324</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>686690</t>
+          <t>686711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1311658</t>
+          <t>1312078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324294</t>
+          <t>1324336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>23213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>36040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500356</t>
+          <t>501372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514527</t>
+          <t>514489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>490895</t>
+          <t>492429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>508334</t>
+          <t>507834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1000177</t>
+          <t>998749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1020229</t>
+          <t>1019545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41215</t>
+          <t>41612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25557</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48635</t>
+          <t>49031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49691</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81143</t>
+          <t>84138</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345495</t>
+          <t>345098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>366967</t>
+          <t>366608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>355351</t>
+          <t>354955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>378429</t>
+          <t>378784</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709553</t>
+          <t>706558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>741005</t>
+          <t>738830</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41342</t>
+          <t>41489</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67609</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56842</t>
+          <t>57340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87493</t>
+          <t>87099</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265944</t>
+          <t>265035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281463</t>
+          <t>281789</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275325</t>
+          <t>275389</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>301592</t>
+          <t>301445</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>548024</t>
+          <t>548418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>578675</t>
+          <t>578177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27622</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>50076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43618</t>
+          <t>43356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72304</t>
+          <t>74379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78497</t>
+          <t>78730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114310</t>
+          <t>115415</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>160054</t>
+          <t>159807</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>182261</t>
+          <t>181211</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261604</t>
+          <t>259529</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290290</t>
+          <t>290552</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>429481</t>
+          <t>428376</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>465294</t>
+          <t>465061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77076</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115878</t>
+          <t>114764</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>147850</t>
+          <t>146473</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>199364</t>
+          <t>198455</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>235279</t>
+          <t>236178</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>298426</t>
+          <t>301417</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3159647</t>
+          <t>3160761</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3198449</t>
+          <t>3197225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3179833</t>
+          <t>3180742</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3231347</t>
+          <t>3232724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6356296</t>
+          <t>6353305</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6419443</t>
+          <t>6418544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2198</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8602</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2198</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6738</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2198</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7713</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451155</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453105</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>422463</t>
+          <t>420737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>874732</t>
+          <t>875707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>674887</t>
+          <t>675623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685241</t>
+          <t>685239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>607165</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1283301</t>
+          <t>1283922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294452</t>
+          <t>1294450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>673962</t>
+          <t>675179</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>692700</t>
+          <t>693193</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>703005</t>
+          <t>703169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1371316</t>
+          <t>1370764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1382880</t>
+          <t>1382099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34627</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599347</t>
+          <t>599249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612553</t>
+          <t>612521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588288</t>
+          <t>587593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>605284</t>
+          <t>604449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1194062</t>
+          <t>1194025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1214696</t>
+          <t>1214655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20911</t>
+          <t>20733</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>29372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54347</t>
+          <t>54703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38236</t>
+          <t>39375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67102</t>
+          <t>67857</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>407433</t>
+          <t>407611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422201</t>
+          <t>422072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393453</t>
+          <t>393097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>418258</t>
+          <t>418428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>809042</t>
+          <t>808287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>837908</t>
+          <t>836769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68554</t>
+          <t>69001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53495</t>
+          <t>54322</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86107</t>
+          <t>88821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282967</t>
+          <t>283644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>299665</t>
+          <t>299546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>284505</t>
+          <t>284058</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>313528</t>
+          <t>311303</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>574747</t>
+          <t>572033</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>607359</t>
+          <t>606532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>23401</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47687</t>
+          <t>46962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70854</t>
+          <t>68902</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104208</t>
+          <t>103780</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>100722</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140376</t>
+          <t>139952</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201349</t>
+          <t>202074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224917</t>
+          <t>225635</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>281506</t>
+          <t>281934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>314860</t>
+          <t>316812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>494374</t>
+          <t>494798</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>534028</t>
+          <t>533073</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55242</t>
+          <t>54702</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91401</t>
+          <t>90999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>181182</t>
+          <t>177098</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>235216</t>
+          <t>236451</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>245081</t>
+          <t>246216</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>315223</t>
+          <t>313136</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3327787</t>
+          <t>3328189</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3363946</t>
+          <t>3364486</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3309918</t>
+          <t>3308683</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3363952</t>
+          <t>3368036</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6649099</t>
+          <t>6651186</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6719241</t>
+          <t>6718106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7034,97 +7034,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7887</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1969</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6884</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6908</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556660</t>
+          <t>555657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1147132</t>
+          <t>1148092</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>12637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661944</t>
+          <t>661910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651856</t>
+          <t>652164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660415</t>
+          <t>660418</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1317855</t>
+          <t>1317846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328483</t>
+          <t>1327704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>32447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>636533</t>
+          <t>637303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644970</t>
+          <t>644967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>620190</t>
+          <t>620478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>638685</t>
+          <t>639600</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1261397</t>
+          <t>1262678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1282185</t>
+          <t>1281965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>19826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>18698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41532</t>
+          <t>39173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27323</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52846</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457678</t>
+          <t>458092</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472840</t>
+          <t>473246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>455317</t>
+          <t>457676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>478318</t>
+          <t>478151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>921921</t>
+          <t>921453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>947444</t>
+          <t>948502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47219</t>
+          <t>47564</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>33249</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58564</t>
+          <t>59159</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>317266</t>
+          <t>316888</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329239</t>
+          <t>329472</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>330543</t>
+          <t>330198</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>352896</t>
+          <t>352806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>653528</t>
+          <t>652933</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>678524</t>
+          <t>678843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>28684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61739</t>
+          <t>62663</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53912</t>
+          <t>51249</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87161</t>
+          <t>83174</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>227338</t>
+          <t>228314</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243875</t>
+          <t>243701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>338430</t>
+          <t>337506</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>365196</t>
+          <t>365341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570006</t>
+          <t>573993</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>603255</t>
+          <t>605918</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>33114</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60827</t>
+          <t>59638</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110223</t>
+          <t>111719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>158235</t>
+          <t>159042</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>154896</t>
+          <t>152690</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>209063</t>
+          <t>209726</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3333523</t>
+          <t>3334712</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3360125</t>
+          <t>3361236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3386307</t>
+          <t>3385500</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3434319</t>
+          <t>3432823</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6729829</t>
+          <t>6729166</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6783996</t>
+          <t>6786202</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4297</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14050</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>4297</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14616</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>14872</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4297</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>16150</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298584</t>
+          <t>299150</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697037</t>
+          <t>698315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417138</t>
+          <t>418196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>502405</t>
+          <t>502617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511359</t>
+          <t>511319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923790</t>
+          <t>923425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933838</t>
+          <t>933850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>16639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528724</t>
+          <t>527605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>529204</t>
+          <t>529115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537903</t>
+          <t>537931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1061566</t>
+          <t>1061291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1072999</t>
+          <t>1072547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23560</t>
+          <t>23146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41732</t>
+          <t>41227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56258</t>
+          <t>56998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>864226</t>
+          <t>864640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883402</t>
+          <t>883480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>671149</t>
+          <t>671654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698483</t>
+          <t>698520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1544409</t>
+          <t>1543669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1580263</t>
+          <t>1580431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21627</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29230</t>
+          <t>29096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47700</t>
+          <t>46706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41298</t>
+          <t>40470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64212</t>
+          <t>62764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>538610</t>
+          <t>538741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>552756</t>
+          <t>552405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>497187</t>
+          <t>498181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>515657</t>
+          <t>515791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1040912</t>
+          <t>1042360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1063826</t>
+          <t>1064654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17602</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82608</t>
+          <t>82975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30666</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84231</t>
+          <t>83597</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>349848</t>
+          <t>349603</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360411</t>
+          <t>360084</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>525760</t>
+          <t>525393</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>588698</t>
+          <t>587507</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>891587</t>
+          <t>892221</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>945152</t>
+          <t>941291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>26113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>49867</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70119</t>
+          <t>70653</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64926</t>
+          <t>67653</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90467</t>
+          <t>91680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255377</t>
+          <t>256156</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>268745</t>
+          <t>269350</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>354275</t>
+          <t>353741</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>373912</t>
+          <t>374527</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>616196</t>
+          <t>614983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>641737</t>
+          <t>639010</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45805</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79269</t>
+          <t>78273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152825</t>
+          <t>153628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>215091</t>
+          <t>214832</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211225</t>
+          <t>212623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>278841</t>
+          <t>282968</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3378346</t>
+          <t>3379342</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3411810</t>
+          <t>3412479</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3441736</t>
+          <t>3441995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3504002</t>
+          <t>3503199</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6835600</t>
+          <t>6831473</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6903216</t>
+          <t>6901818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A09-Edad-trans_orig.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730701</t>
+          <t>730090</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>615378</t>
+          <t>614779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1350044</t>
+          <t>1349422</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360037</t>
+          <t>1360032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>674324</t>
+          <t>674582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>686711</t>
+          <t>686719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312078</t>
+          <t>1312171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324336</t>
+          <t>1324426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36040</t>
+          <t>35607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>501372</t>
+          <t>501442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514489</t>
+          <t>514304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>492429</t>
+          <t>493477</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>507834</t>
+          <t>508323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>998749</t>
+          <t>999182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1019545</t>
+          <t>1019755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20102</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41612</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51866</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84138</t>
+          <t>83300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345098</t>
+          <t>345049</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>366608</t>
+          <t>366677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>354955</t>
+          <t>355342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>378784</t>
+          <t>378402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706558</t>
+          <t>707396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>738830</t>
+          <t>740273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67545</t>
+          <t>65934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57340</t>
+          <t>56541</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87099</t>
+          <t>86836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265035</t>
+          <t>266428</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281789</t>
+          <t>282202</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275389</t>
+          <t>277000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>301445</t>
+          <t>302195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>548418</t>
+          <t>548681</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>578177</t>
+          <t>578976</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28672</t>
+          <t>27955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50076</t>
+          <t>48541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43356</t>
+          <t>43333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74379</t>
+          <t>74523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78730</t>
+          <t>77608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115415</t>
+          <t>112501</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>159807</t>
+          <t>161342</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>181211</t>
+          <t>181928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>259529</t>
+          <t>259385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290552</t>
+          <t>290575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>428376</t>
+          <t>431290</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>465061</t>
+          <t>466183</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78300</t>
+          <t>78523</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>114764</t>
+          <t>115374</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146473</t>
+          <t>147081</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>198455</t>
+          <t>200905</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>236178</t>
+          <t>235431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>301417</t>
+          <t>299774</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3160761</t>
+          <t>3160151</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3197225</t>
+          <t>3197002</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3180742</t>
+          <t>3178292</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3232724</t>
+          <t>3232116</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6353305</t>
+          <t>6354948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6418544</t>
+          <t>6419291</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420737</t>
+          <t>421539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875707</t>
+          <t>875702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4055,82 +4055,82 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11542</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>999</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10615</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3873</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>675623</t>
+          <t>674696</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685239</t>
+          <t>685240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1283922</t>
+          <t>1283061</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294450</t>
+          <t>1294452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15225</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>675179</t>
+          <t>675197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>693193</t>
+          <t>691313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>703169</t>
+          <t>702908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1370764</t>
+          <t>1371150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1382099</t>
+          <t>1382122</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26479</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34664</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599249</t>
+          <t>599795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612521</t>
+          <t>612536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>587593</t>
+          <t>588134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>604449</t>
+          <t>604267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1194025</t>
+          <t>1193581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1214655</t>
+          <t>1214537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54703</t>
+          <t>54759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39375</t>
+          <t>39372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67857</t>
+          <t>69439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>407611</t>
+          <t>407205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422072</t>
+          <t>422537</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393097</t>
+          <t>393041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>418428</t>
+          <t>418636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>808287</t>
+          <t>806705</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>836769</t>
+          <t>836772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24151</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41756</t>
+          <t>41744</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69001</t>
+          <t>69259</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54322</t>
+          <t>53316</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88821</t>
+          <t>85990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283644</t>
+          <t>284096</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>299546</t>
+          <t>299705</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>284058</t>
+          <t>283800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>311303</t>
+          <t>311315</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>572033</t>
+          <t>574864</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>606532</t>
+          <t>607538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>23678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46962</t>
+          <t>48061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68902</t>
+          <t>69447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103780</t>
+          <t>104705</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>100680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139952</t>
+          <t>140331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>202074</t>
+          <t>200975</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225635</t>
+          <t>225358</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>281934</t>
+          <t>281009</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316812</t>
+          <t>316267</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>494798</t>
+          <t>494419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>533073</t>
+          <t>534070</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54702</t>
+          <t>56285</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90999</t>
+          <t>91026</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177098</t>
+          <t>178549</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>236451</t>
+          <t>236700</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246216</t>
+          <t>247370</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>313136</t>
+          <t>309906</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3328189</t>
+          <t>3328162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3364486</t>
+          <t>3362903</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3308683</t>
+          <t>3308434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3368036</t>
+          <t>3366585</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6651186</t>
+          <t>6654416</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6718106</t>
+          <t>6716952</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555657</t>
+          <t>557284</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1148092</t>
+          <t>1147159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661910</t>
+          <t>661818</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652164</t>
+          <t>652006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660418</t>
+          <t>660406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1317846</t>
+          <t>1318378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327704</t>
+          <t>1327709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28599</t>
+          <t>29468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>32902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637303</t>
+          <t>637276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644967</t>
+          <t>644971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>620478</t>
+          <t>619609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>639600</t>
+          <t>638144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1262678</t>
+          <t>1262223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1281965</t>
+          <t>1281752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19826</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39173</t>
+          <t>39892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53314</t>
+          <t>51900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458092</t>
+          <t>456572</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473246</t>
+          <t>473019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>457676</t>
+          <t>456957</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>478151</t>
+          <t>479155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>921453</t>
+          <t>922867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>948502</t>
+          <t>947662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24956</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47564</t>
+          <t>48358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33249</t>
+          <t>33091</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59159</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>316888</t>
+          <t>317195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329472</t>
+          <t>329389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>330198</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>352806</t>
+          <t>353053</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>652933</t>
+          <t>653137</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>678843</t>
+          <t>679001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34828</t>
+          <t>34861</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62663</t>
+          <t>61802</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51249</t>
+          <t>52763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83174</t>
+          <t>86990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228314</t>
+          <t>229087</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243701</t>
+          <t>244025</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337506</t>
+          <t>338367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>365341</t>
+          <t>365308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>573993</t>
+          <t>570177</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>605918</t>
+          <t>604404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59638</t>
+          <t>60175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111719</t>
+          <t>110235</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159042</t>
+          <t>158867</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152690</t>
+          <t>154872</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>209726</t>
+          <t>206987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3334712</t>
+          <t>3334175</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3361236</t>
+          <t>3361264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3385500</t>
+          <t>3385675</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3432823</t>
+          <t>3434307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6729166</t>
+          <t>6731905</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6786202</t>
+          <t>6784020</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>308903</t>
+          <t>357399</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299150</t>
+          <t>344814</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>708890</t>
+          <t>765192</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698315</t>
+          <t>751481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,22 +10078,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>422279</t>
+          <t>475525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418196</t>
+          <t>469454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>508889</t>
+          <t>497643</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>502617</t>
+          <t>490680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511319</t>
+          <t>500006</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,27 +10191,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>931167</t>
+          <t>973168</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923425</t>
+          <t>967134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933850</t>
+          <t>976732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,27 +10386,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10421,22 +10421,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -10464,27 +10464,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>533941</t>
+          <t>618340</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527605</t>
+          <t>613261</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10499,22 +10499,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>534408</t>
+          <t>612942</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>529115</t>
+          <t>606990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537931</t>
+          <t>617221</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,27 +10534,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1068349</t>
+          <t>1231281</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1061291</t>
+          <t>1224344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1072547</t>
+          <t>1235858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541592</t>
+          <t>621267</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541592</t>
+          <t>621267</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541592</t>
+          <t>621267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077930</t>
+          <t>1242103</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077930</t>
+          <t>1242103</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077930</t>
+          <t>1242103</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41227</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>36022</t>
+          <t>33782</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56998</t>
+          <t>46691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>874974</t>
+          <t>687237</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>864640</t>
+          <t>677305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883480</t>
+          <t>693196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>689670</t>
+          <t>716484</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>671654</t>
+          <t>708398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698520</t>
+          <t>723280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1564645</t>
+          <t>1403722</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1543669</t>
+          <t>1390813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1580431</t>
+          <t>1412886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,17 +11037,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37533</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29096</t>
+          <t>33518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46706</t>
+          <t>52236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51006</t>
+          <t>56405</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40470</t>
+          <t>44411</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62764</t>
+          <t>68699</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -11150,17 +11150,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>546764</t>
+          <t>593744</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>538741</t>
+          <t>583502</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>552405</t>
+          <t>599538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>507354</t>
+          <t>565658</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>498181</t>
+          <t>555212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>515791</t>
+          <t>573930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1054118</t>
+          <t>1159402</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1042360</t>
+          <t>1147108</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1064654</t>
+          <t>1171396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17847</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51818</t>
+          <t>58199</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>47881</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82975</t>
+          <t>69187</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>63414</t>
+          <t>71034</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34527</t>
+          <t>59788</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83597</t>
+          <t>83243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -11493,17 +11493,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>355853</t>
+          <t>393433</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>349603</t>
+          <t>387027</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360084</t>
+          <t>398577</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>556550</t>
+          <t>380967</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>525393</t>
+          <t>369979</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>587507</t>
+          <t>391285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>912404</t>
+          <t>774401</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>892221</t>
+          <t>762192</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>941291</t>
+          <t>785647</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367450</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367450</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367450</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975818</t>
+          <t>845435</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975818</t>
+          <t>845435</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975818</t>
+          <t>845435</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>13910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26113</t>
+          <t>29277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>59674</t>
+          <t>66466</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49867</t>
+          <t>54251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70653</t>
+          <t>77667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>78736</t>
+          <t>87575</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67653</t>
+          <t>73603</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91680</t>
+          <t>100801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>263207</t>
+          <t>288594</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>256156</t>
+          <t>280426</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>269350</t>
+          <t>295793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>364720</t>
+          <t>396613</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>353741</t>
+          <t>385412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>374527</t>
+          <t>408828</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>627927</t>
+          <t>685207</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>614983</t>
+          <t>671981</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>639010</t>
+          <t>699179</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>65800</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45136</t>
+          <t>52578</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78273</t>
+          <t>83495</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>186333</t>
+          <t>203735</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153628</t>
+          <t>182405</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>214832</t>
+          <t>226977</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>246942</t>
+          <t>269535</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>212623</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282968</t>
+          <t>296333</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3397006</t>
+          <t>3464669</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3379342</t>
+          <t>3446974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3412479</t>
+          <t>3477891</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3470494</t>
+          <t>3527706</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3441995</t>
+          <t>3504464</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3503199</t>
+          <t>3549036</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6867499</t>
+          <t>6992375</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6831473</t>
+          <t>6965577</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6901818</t>
+          <t>7018956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457615</t>
+          <t>3530469</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457615</t>
+          <t>3530469</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457615</t>
+          <t>3530469</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3656827</t>
+          <t>3731441</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3656827</t>
+          <t>3731441</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656827</t>
+          <t>3731441</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7114441</t>
+          <t>7261910</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7114441</t>
+          <t>7261910</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7114441</t>
+          <t>7261910</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
